--- a/data/daily/2026-10/2026-10-02.xlsx
+++ b/data/daily/2026-10/2026-10-02.xlsx
@@ -1220,14 +1220,89 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="342900" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="342900" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>5</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="342900" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>6</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="381000" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="3" name="Image 3" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1242,17 +1317,17 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>4</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="323850" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
+      <row>7</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="342900" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1267,17 +1342,17 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>5</row>
+      <row>8</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="342900" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1292,110 +1367,35 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>6</row>
+      <row>9</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>10</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="342900" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>7</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="342900" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>8</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="342900" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="8" name="Image 8" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>9</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="457200" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="9" name="Image 9" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>10</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="381000" cy="457200"/>
     <pic>
       <nvPicPr>
         <cNvPr id="10" name="Image 10" descr="Picture"/>
@@ -1475,52 +1475,127 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="933450" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="933450" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="933450" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="1028700" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="3" name="Image 3" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="866775" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>6</col>
+    <ext cx="933450" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
@@ -1528,129 +1603,54 @@
     <ext cx="933450" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>7</col>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>11</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="933450" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="933450" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>9</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="933450" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="8" name="Image 8" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>10</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1238250" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="9" name="Image 9" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>11</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1028700" cy="1238250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="10" name="Image 10" descr="Picture"/>
@@ -2596,23 +2596,11 @@
         <v>4</v>
       </c>
       <c r="J2" t="n">
-        <v>16197</v>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>선물용 높은 만족도 — 정성스러운 포장과 높은 구성으로 선물 시 만족도가 매우 높음</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>피로 회복 효과 — 섭취 후 피로감이 줄어들고 활력을 얻는 데 도움을 줌</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>간편한 휴대 및 섭취 — 하나씩 가볍게 휴대하며 챙겨 먹기 편리함</t>
-        </is>
-      </c>
+        <v>16198</v>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
@@ -2655,29 +2643,13 @@
         <v>4</v>
       </c>
       <c r="J3" t="n">
-        <v>15517</v>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>피로 개선 및 활력 증진 — 섭취 후 체력이 좋아지고 몸이 가뿐해지는 느낌을 받음</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>깔끔한 선물용 패키지 — 패키지 박스가 예쁘고 깔끔하여 선물용으로 적합함</t>
-        </is>
-      </c>
+        <v>15518</v>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>다소 비싼 가격대 — 제품 가격이 다소 비싸게 느껴짐</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>배송 지연 발생 — 배송이 다소 느리게 진행됨</t>
-        </is>
-      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
     </row>
     <row r="4" ht="38" customHeight="1">
@@ -2720,22 +2692,10 @@
       <c r="J4" t="n">
         <v>3387</v>
       </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>고급스러운 포장 디자인 — 포장이 깔끔하고 고급스러워 선물용으로 매우 만족스러움</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>체력 및 건강 관리 효과 — 피로 회복 및 면역력 관리에 효과적임</t>
-        </is>
-      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>발송자 확인 불편 — 선물 보낸 사람 정보 확인이 어렵고 문의 응대가 아쉬움</t>
-        </is>
-      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
     </row>
@@ -2779,16 +2739,8 @@
       <c r="J5" t="n">
         <v>6495</v>
       </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>맛있는 과일 맛 젤리 — 새콤달콤한 과일 향과 맛으로 거부감 없이 맛있게 먹기 좋음</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>간편한 섭취 방식 — 알약을 잘 못 먹는 사람도 물 없이 편하게 먹을 수 있음</t>
-        </is>
-      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
@@ -2805,45 +2757,37 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>독일 명품 비타민 오쏘몰 이뮨 멀티비타민&amp;미네랄 10입 - 추석 기프트 에디션 (공식수입)</t>
+          <t>명품 비타민 뉴트리포유 듀얼+ 이뮨 종합 멀티비타민&amp;미네랄 7입+2입 증정 - 선물하기 단독 에디션</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>오쏘몰</t>
+          <t>뉴트리포유</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>43,900원</t>
+          <t>19,900원</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/11866425</t>
+          <t>https://gift.kakao.com/product/10056171</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260831093017_c95c591e7b5b4e3d9e549888b299930a.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260219100848_1c2cc8073bd44eaab9f09d6b8fb8f34c.jpg</t>
         </is>
       </c>
       <c r="I6" t="n">
         <v>4</v>
       </c>
       <c r="J6" t="n">
-        <v>807</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>고급스러운 선물 패키지 — 박스와 종이가방 포장이 고급스러워 명절 선물로 적합함</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>피로 회복 및 면역 케어 — 섭취 후 피로감이 줄어들고 하루 에너지를 유지하는 데 도움을 줌</t>
-        </is>
-      </c>
+        <v>8739</v>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -2860,45 +2804,37 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>명품 비타민 뉴트리포유 듀얼+ 이뮨 종합 멀티비타민&amp;미네랄 7입+2입 증정 - 선물하기 단독 에디션</t>
+          <t>독일 명품 비타민 오쏘몰 이뮨 멀티비타민&amp;미네랄 10입 - 추석 기프트 에디션 (공식수입)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>뉴트리포유</t>
+          <t>오쏘몰</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>19,900원</t>
+          <t>43,900원</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/10056171</t>
+          <t>https://gift.kakao.com/product/11866425</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260219100848_1c2cc8073bd44eaab9f09d6b8fb8f34c.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260831093017_c95c591e7b5b4e3d9e549888b299930a.jpg</t>
         </is>
       </c>
       <c r="I7" t="n">
         <v>4</v>
       </c>
       <c r="J7" t="n">
-        <v>8738</v>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>기력 회복 및 피로 완화 — 섭취 시 아침 컨디션이 개선되고 피로 회복에 도움을 줌</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>간편한 섭취와 증정 구성 — 추가 증정 구성이 알차고 바쁜 일상에서 챙겨 먹기 편함</t>
-        </is>
-      </c>
+        <v>807</v>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
@@ -2942,23 +2878,11 @@
         <v>4</v>
       </c>
       <c r="J8" t="n">
-        <v>1724</v>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>달콤하고 부드러운 맛 — 쓴맛 없이 달달하여 어르신들도 부담 없이 먹기 좋음</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>고급스러운 패키지 — 포장 상태가 고급스러워 건강 선물용으로 적합함</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>물 없는 간편한 섭취 — 휴대가 용이하고 물 없이도 간편하게 먹을 수 있음</t>
-        </is>
-      </c>
+        <v>1723</v>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
@@ -3001,29 +2925,13 @@
         <v>4</v>
       </c>
       <c r="J9" t="n">
-        <v>803</v>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>하루 활력 충전 — 아침에 섭취 시 하루 동안의 활력 증진에 도움을 줌</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>높은 선물 만족도 — 유명 제품으로 선물 시 받는 사람의 만족도가 높음</t>
-        </is>
-      </c>
+        <v>804</v>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>높은 당 함량 — 당 함유량이 4g으로 다소 높게 느껴짐</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>가격 부담감 — 가격대가 높아 직접 구매하기에 부담스러움</t>
-        </is>
-      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
     </row>
     <row r="10" ht="38" customHeight="1">
@@ -3066,22 +2974,10 @@
       <c r="J10" t="n">
         <v>776</v>
       </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>성별 맞춤 옵션 — 남성용과 여성용 제품을 구분하여 선택할 수 있음</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>피로 개선 효과 — 쓴맛이 적고 꾸준히 복용 시 피로가 개선됨</t>
-        </is>
-      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>알약 크기의 부담 — 기존 제품 대비 알약이 크아 삼키기 다소 힘듦</t>
-        </is>
-      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
     </row>
@@ -3125,27 +3021,11 @@
       <c r="J11" t="n">
         <v>220</v>
       </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>피로감 감소 효능 — 섭취 시 피로가 줄어들어 자주 챙겨 먹게 됨</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>선물용 우수성 — 선물용으로 추천하기에 만족도가 높음</t>
-        </is>
-      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>포장 위생 상태 아쉬움 — 상자와 쇼핑백에 먼지가 많이 묻은 상태로 배송됨</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>배송 지연 발생 — 배송이 일부 지연되어 도착함</t>
-        </is>
-      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
     </row>
     <row r="12" ht="38" customHeight="1">
@@ -3186,28 +3066,12 @@
         <v>4</v>
       </c>
       <c r="J12" t="n">
-        <v>106</v>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>맛있는 맛과 식감 — 베리말차 맛 등이 뛰어나고 씹히는 느낌이 좋아 맛있게 먹을 수 있음</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>속 편한 소화 효과 — 더부룩함이 줄어들고 소화가 잘되어 속이 편안함</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>알찬 굿즈 및 사은품 — 포토카드와 단백질바 증정 등으로 구성 가성비가 좋음</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>다소 느린 배송 — 배송 도착까지의 시간이 다소 걸림</t>
-        </is>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr"/>
     </row>
@@ -3251,22 +3115,10 @@
       <c r="J13" t="n">
         <v>1682</v>
       </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>구수한 고구마 맛 — 거부감 없는 구수한 고구마 맛으로 맛있는 섭취 가능함</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>소화 및 편안한 속 — 속을 편하게 해주며 소화 및 배변 활동에 도움을 줌</t>
-        </is>
-      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>증정품 용량 아쉬움 — 증정으로 제공된 단백질칩의 크기가 다소 작음</t>
-        </is>
-      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr"/>
     </row>
@@ -3308,24 +3160,12 @@
         <v>4</v>
       </c>
       <c r="J14" t="n">
-        <v>751</v>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>예쁘고 고급스러운 포장 — 포장이 매우 고급스럽고 예뻐 선물 시 기분이 좋아짐</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>편리한 개별 앰플 — 낱개 앰플 형태로 되어 있어 하나씩 따서 마시기 편함</t>
-        </is>
-      </c>
+        <v>752</v>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>높은 가격대 — 가격이 다소 비싸 할인 시 구매를 고려하게 됨</t>
-        </is>
-      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
     </row>
@@ -3369,27 +3209,11 @@
       <c r="J15" t="n">
         <v>152</v>
       </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>높은 포만감과 뛰어난 맛 — 맛이 좋으며 한 개만 먹어도 포만감이 오래 유지됨</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>다양한 구성 — 여러 종류의 메뉴가 포함되어 매일 다르게 먹기 좋음</t>
-        </is>
-      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>오배송 및 구성 누락 — 주문한 구성과 다르게 제품이 중복 오배송됨</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>포장 터짐 및 누수 — 비닐 포장이 헐겁거나 터져 소스가 새어 나옴</t>
-        </is>
-      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
     </row>
     <row r="16" ht="38" customHeight="1">
@@ -3432,26 +3256,10 @@
       <c r="J16" t="n">
         <v>60</v>
       </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>부드러운 식감과 맛 — 닭가슴살 특유의 퍽퍽함 없이 부드럽고 맛있음</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>다양한 맛과 제형 — 스테이크, 볼, 주먹밥 등 다양한 구성으로 질리지 않음</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>우수한 가성비 — 할인가 기준으로 알찬 구성 대비 가격 만족도가 높음</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>선호 옵션 미포함 — 인기 있는 파우치형 그릴 제품이 구성에 없어 아쉬움</t>
-        </is>
-      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
     </row>
@@ -3495,22 +3303,10 @@
       <c r="J17" t="n">
         <v>69</v>
       </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>촉촉하고 쫄깃한 식감 — 퍽퍽하지 않고 촉촉하며 간이 적당해 부담 없이 먹기 좋음</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>간편한 조리 방법 — 전자레인지에 간단히 데워 바로 먹을 수 있어 편리함</t>
-        </is>
-      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>다소 느린 배송 — 배송 도착 속도가 다소 느린 편임</t>
-        </is>
-      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr"/>
     </row>
@@ -3554,16 +3350,8 @@
       <c r="J18" t="n">
         <v>217</v>
       </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>비린 맛 없는 음료 맛 — 단백질 음료 특유의 비린 맛이나 텁텁함 없이 달콤함</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>운동 후 포만감 — 운동 후 마시기에 적합하며 섭취 후 배가 고프지 않음</t>
-        </is>
-      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
@@ -3572,7 +3360,7 @@
     <row r="19" ht="38" customHeight="1">
       <c r="B19" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -3580,50 +3368,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>아르기닌 증정 남친 활력선물 대한민국 NO.1 김종국 트리플아르기닌 6200 (30포) + 아르기닌 추가 증정</t>
+          <t>편안한 밤 필수템 식물성 멜라토닌 1mg 구미 젤리 멜라메이트 1박스 (50구미) 수험생/직장인 선물</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>익스트림</t>
+          <t>CJ웰케어</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>43,900원</t>
+          <t>18,900원</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/7417420</t>
+          <t>https://gift.kakao.com/product/12065660</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260706153340_3e124da6e254462d9a7efad2521e3b9e.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260126092430_c053db53f3d44b89900041b9c7968dc9.jpg</t>
         </is>
       </c>
       <c r="I19" t="n">
         <v>4</v>
       </c>
       <c r="J19" t="n">
-        <v>248</v>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>고함량 체력 증진 — 6,200mg 고함량 아르기닌으로 활력 향상 및 피로 완화에 효과적임</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>휴대성 및 섭취 간편성 — 1회용 개별 스틱 포장으로 휴대하며 쉽게 챙겨 먹을 수 있음</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>고급스러운 packaging — 쇼핑백과 고급스러운 디자인으로 선물용에 적합함</t>
-        </is>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
@@ -3631,7 +3407,7 @@
     <row r="20" ht="38" customHeight="1">
       <c r="B20" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -3639,55 +3415,39 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>[단독] 알디콤Plus 숙취해소제 선물세트 (5포입x3개)</t>
+          <t>아르기닌 증정 남친 활력선물 대한민국 NO.1 김종국 트리플아르기닌 6200 (30포) + 아르기닌 추가 증정</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>알디콤</t>
+          <t>익스트림</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>33,200원</t>
+          <t>43,900원</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/12064702</t>
+          <t>https://gift.kakao.com/product/7417420</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260827134326_6543fa160cfd4c4294103fd47b3d0a12.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260706153340_3e124da6e254462d9a7efad2521e3b9e.jpg</t>
         </is>
       </c>
       <c r="I20" t="n">
         <v>4</v>
       </c>
       <c r="J20" t="n">
-        <v>21</v>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>확실한 숙취 해소 효과 — 음주 전후 섭취 시 다음 날 아침 숙취가 현저히 감소함</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>간편한 휴대와 섭취 — 작은 스틱 타입이라 가방에 넣기 편하고 물 없이 먹을 수 있음</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>고급스러운 선물용 포장 — 리본 손잡이가 달린 쇼핑백 형태 포장이라 선물용으로 우수함</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>한약 맛 호불호 — 쌍화탕이나 한약재 특유의 맛이 나 취향을 탈 수 있음</t>
-        </is>
-      </c>
+        <v>248</v>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr"/>
     </row>
@@ -3702,51 +3462,39 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>편안한 밤 필수템 식물성 멜라토닌 1mg 구미 젤리 멜라메이트 1박스 (50구미) 수험생/직장인 선물</t>
+          <t>[단독] 알디콤Plus 숙취해소제 선물세트 (5포입x3개)</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>CJ웰케어</t>
+          <t>알디콤</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>18,900원</t>
+          <t>33,200원</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/12065660</t>
+          <t>https://gift.kakao.com/product/12064702</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260126092430_c053db53f3d44b89900041b9c7968dc9.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260827134326_6543fa160cfd4c4294103fd47b3d0a12.jpg</t>
         </is>
       </c>
       <c r="I21" t="n">
         <v>4</v>
       </c>
       <c r="J21" t="n">
-        <v>39</v>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>수면 진입 및 숙면 도움 — 자기 전 섭취 시 자연스럽게 졸음이 오고 수면 유지에 도움을 줌</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>맛있는 과일 맛 구미 — 상큼한 과일 맛의 젤리 형태로 간식처럼 부담 없이 먹기 좋음</t>
-        </is>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>취침 전 당분 부담 — 설탕과 물엿이 함유되어 잠들기 전 섭취 시 당분이 부담스러움</t>
-        </is>
-      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr"/>
     </row>
@@ -3938,12 +3686,12 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
+          <t>뉴트리포유</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
           <t>오쏘몰</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>뉴트리포유</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
@@ -3995,12 +3743,12 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
+          <t>명품 비타민 뉴트리포유 듀얼+ 이뮨 종합 멀티비타민&amp;미네랄 7입+2입 증정 - 선물하기 단독 에디션</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
           <t>독일 명품 비타민 오쏘몰 이뮨 멀티비타민&amp;미네랄 10입 - 추석 기프트 에디션 (공식수입)</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>명품 비타민 뉴트리포유 듀얼+ 이뮨 종합 멀티비타민&amp;미네랄 7입+2입 증정 - 선물하기 단독 에디션</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
@@ -4068,10 +3816,10 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>16197</v>
+        <v>16198</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>15517</v>
+        <v>15518</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>3387</v>
@@ -4080,16 +3828,16 @@
         <v>6495</v>
       </c>
       <c r="G7" s="3" t="n">
+        <v>8739</v>
+      </c>
+      <c r="H7" s="3" t="n">
         <v>807</v>
       </c>
-      <c r="H7" s="3" t="n">
-        <v>8738</v>
-      </c>
       <c r="I7" s="3" t="n">
-        <v>1724</v>
+        <v>1723</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="K7" s="3" t="n">
         <v>776</v>
@@ -4098,114 +3846,39 @@
         <v>220</v>
       </c>
     </row>
-    <row r="8" ht="90" customHeight="1">
+    <row r="8">
       <c r="B8" s="1" t="inlineStr">
         <is>
           <t>긍정리뷰</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>선물용 높은 만족도 — 정성스러운 포장과 높은 구성으로 선물 시 만족도가 매우 높음
-피로 회복 효과 — 섭취 후 피로감이 줄어들고 활력을 얻는 데 도움을 줌
-간편한 휴대 및 섭취 — 하나씩 가볍게 휴대하며 챙겨 먹기 편리함</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>피로 개선 및 활력 증진 — 섭취 후 체력이 좋아지고 몸이 가뿐해지는 느낌을 받음
-깔끔한 선물용 패키지 — 패키지 박스가 예쁘고 깔끔하여 선물용으로 적합함</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>고급스러운 포장 디자인 — 포장이 깔끔하고 고급스러워 선물용으로 매우 만족스러움
-체력 및 건강 관리 효과 — 피로 회복 및 면역력 관리에 효과적임</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>맛있는 과일 맛 젤리 — 새콤달콤한 과일 향과 맛으로 거부감 없이 맛있게 먹기 좋음
-간편한 섭취 방식 — 알약을 잘 못 먹는 사람도 물 없이 편하게 먹을 수 있음</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>고급스러운 선물 패키지 — 박스와 종이가방 포장이 고급스러워 명절 선물로 적합함
-피로 회복 및 면역 케어 — 섭취 후 피로감이 줄어들고 하루 에너지를 유지하는 데 도움을 줌</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>기력 회복 및 피로 완화 — 섭취 시 아침 컨디션이 개선되고 피로 회복에 도움을 줌
-간편한 섭취와 증정 구성 — 추가 증정 구성이 알차고 바쁜 일상에서 챙겨 먹기 편함</t>
-        </is>
-      </c>
-      <c r="I8" s="3" t="inlineStr">
-        <is>
-          <t>달콤하고 부드러운 맛 — 쓴맛 없이 달달하여 어르신들도 부담 없이 먹기 좋음
-고급스러운 패키지 — 포장 상태가 고급스러워 건강 선물용으로 적합함
-물 없는 간편한 섭취 — 휴대가 용이하고 물 없이도 간편하게 먹을 수 있음</t>
-        </is>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>하루 활력 충전 — 아침에 섭취 시 하루 동안의 활력 증진에 도움을 줌
-높은 선물 만족도 — 유명 제품으로 선물 시 받는 사람의 만족도가 높음</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
-          <t>성별 맞춤 옵션 — 남성용과 여성용 제품을 구분하여 선택할 수 있음
-피로 개선 효과 — 쓴맛이 적고 꾸준히 복용 시 피로가 개선됨</t>
-        </is>
-      </c>
-      <c r="L8" s="3" t="inlineStr">
-        <is>
-          <t>피로감 감소 효능 — 섭취 시 피로가 줄어들어 자주 챙겨 먹게 됨
-선물용 우수성 — 선물용으로 추천하기에 만족도가 높음</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="60" customHeight="1">
+      <c r="C8" s="3" t="inlineStr"/>
+      <c r="D8" s="3" t="inlineStr"/>
+      <c r="E8" s="3" t="inlineStr"/>
+      <c r="F8" s="3" t="inlineStr"/>
+      <c r="G8" s="3" t="inlineStr"/>
+      <c r="H8" s="3" t="inlineStr"/>
+      <c r="I8" s="3" t="inlineStr"/>
+      <c r="J8" s="3" t="inlineStr"/>
+      <c r="K8" s="3" t="inlineStr"/>
+      <c r="L8" s="3" t="inlineStr"/>
+    </row>
+    <row r="9">
       <c r="B9" s="1" t="inlineStr">
         <is>
           <t>부정리뷰</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr"/>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>다소 비싼 가격대 — 제품 가격이 다소 비싸게 느껴짐
-배송 지연 발생 — 배송이 다소 느리게 진행됨</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>발송자 확인 불편 — 선물 보낸 사람 정보 확인이 어렵고 문의 응대가 아쉬움</t>
-        </is>
-      </c>
+      <c r="D9" s="3" t="inlineStr"/>
+      <c r="E9" s="3" t="inlineStr"/>
       <c r="F9" s="3" t="inlineStr"/>
       <c r="G9" s="3" t="inlineStr"/>
       <c r="H9" s="3" t="inlineStr"/>
       <c r="I9" s="3" t="inlineStr"/>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>높은 당 함량 — 당 함유량이 4g으로 다소 높게 느껴짐
-가격 부담감 — 가격대가 높아 직접 구매하기에 부담스러움</t>
-        </is>
-      </c>
-      <c r="K9" s="3" t="inlineStr">
-        <is>
-          <t>알약 크기의 부담 — 기존 제품 대비 알약이 크아 삼키기 다소 힘듦</t>
-        </is>
-      </c>
-      <c r="L9" s="3" t="inlineStr">
-        <is>
-          <t>포장 위생 상태 아쉬움 — 상자와 쇼핑백에 먼지가 많이 묻은 상태로 배송됨
-배송 지연 발생 — 배송이 일부 지연되어 도착함</t>
-        </is>
-      </c>
+      <c r="J9" s="3" t="inlineStr"/>
+      <c r="K9" s="3" t="inlineStr"/>
+      <c r="L9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="B10" s="1" t="inlineStr">
@@ -4235,12 +3908,12 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
+          <t>19,900원</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
           <t>43,900원</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>19,900원</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
@@ -4438,12 +4111,12 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
           <t>다이어트/체중관리</t>
-        </is>
-      </c>
-      <c r="K15" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
@@ -4495,17 +4168,17 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
+          <t>CJ웰케어</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
           <t>익스트림</t>
         </is>
       </c>
-      <c r="K16" s="3" t="inlineStr">
+      <c r="L16" s="3" t="inlineStr">
         <is>
           <t>알디콤</t>
-        </is>
-      </c>
-      <c r="L16" s="3" t="inlineStr">
-        <is>
-          <t>CJ웰케어</t>
         </is>
       </c>
     </row>
@@ -4552,17 +4225,17 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
+          <t>편안한 밤 필수템 식물성 멜라토닌 1mg 구미 젤리 멜라메이트 1박스 (50구미) 수험생/직장인 선물</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
           <t>아르기닌 증정 남친 활력선물 대한민국 NO.1 김종국 트리플아르기닌 6200 (30포) + 아르기닌 추가 증정</t>
         </is>
       </c>
-      <c r="K17" s="3" t="inlineStr">
+      <c r="L17" s="3" t="inlineStr">
         <is>
           <t>[단독] 알디콤Plus 숙취해소제 선물세트 (5포입x3개)</t>
-        </is>
-      </c>
-      <c r="L17" s="3" t="inlineStr">
-        <is>
-          <t>편안한 밤 필수템 식물성 멜라토닌 1mg 구미 젤리 멜라메이트 1박스 (50구미) 수험생/직장인 선물</t>
         </is>
       </c>
     </row>
@@ -4610,13 +4283,13 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>1682</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="F19" s="3" t="n">
         <v>152</v>
@@ -4631,135 +4304,48 @@
         <v>217</v>
       </c>
       <c r="J19" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="K19" s="3" t="n">
         <v>248</v>
       </c>
-      <c r="K19" s="3" t="n">
+      <c r="L19" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="L19" s="3" t="n">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="20" ht="90" customHeight="1">
+    </row>
+    <row r="20">
       <c r="B20" s="1" t="inlineStr">
         <is>
           <t>긍정리뷰</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>맛있는 맛과 식감 — 베리말차 맛 등이 뛰어나고 씹히는 느낌이 좋아 맛있게 먹을 수 있음
-속 편한 소화 효과 — 더부룩함이 줄어들고 소화가 잘되어 속이 편안함
-알찬 굿즈 및 사은품 — 포토카드와 단백질바 증정 등으로 구성 가성비가 좋음</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>구수한 고구마 맛 — 거부감 없는 구수한 고구마 맛으로 맛있는 섭취 가능함
-소화 및 편안한 속 — 속을 편하게 해주며 소화 및 배변 활동에 도움을 줌</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="inlineStr">
-        <is>
-          <t>예쁘고 고급스러운 포장 — 포장이 매우 고급스럽고 예뻐 선물 시 기분이 좋아짐
-편리한 개별 앰플 — 낱개 앰플 형태로 되어 있어 하나씩 따서 마시기 편함</t>
-        </is>
-      </c>
-      <c r="F20" s="3" t="inlineStr">
-        <is>
-          <t>높은 포만감과 뛰어난 맛 — 맛이 좋으며 한 개만 먹어도 포만감이 오래 유지됨
-다양한 구성 — 여러 종류의 메뉴가 포함되어 매일 다르게 먹기 좋음</t>
-        </is>
-      </c>
-      <c r="G20" s="3" t="inlineStr">
-        <is>
-          <t>부드러운 식감과 맛 — 닭가슴살 특유의 퍽퍽함 없이 부드럽고 맛있음
-다양한 맛과 제형 — 스테이크, 볼, 주먹밥 등 다양한 구성으로 질리지 않음
-우수한 가성비 — 할인가 기준으로 알찬 구성 대비 가격 만족도가 높음</t>
-        </is>
-      </c>
-      <c r="H20" s="3" t="inlineStr">
-        <is>
-          <t>촉촉하고 쫄깃한 식감 — 퍽퍽하지 않고 촉촉하며 간이 적당해 부담 없이 먹기 좋음
-간편한 조리 방법 — 전자레인지에 간단히 데워 바로 먹을 수 있어 편리함</t>
-        </is>
-      </c>
-      <c r="I20" s="3" t="inlineStr">
-        <is>
-          <t>비린 맛 없는 음료 맛 — 단백질 음료 특유의 비린 맛이나 텁텁함 없이 달콤함
-운동 후 포만감 — 운동 후 마시기에 적합하며 섭취 후 배가 고프지 않음</t>
-        </is>
-      </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>고함량 체력 증진 — 6,200mg 고함량 아르기닌으로 활력 향상 및 피로 완화에 효과적임
-휴대성 및 섭취 간편성 — 1회용 개별 스틱 포장으로 휴대하며 쉽게 챙겨 먹을 수 있음
-고급스러운 packaging — 쇼핑백과 고급스러운 디자인으로 선물용에 적합함</t>
-        </is>
-      </c>
-      <c r="K20" s="3" t="inlineStr">
-        <is>
-          <t>확실한 숙취 해소 효과 — 음주 전후 섭취 시 다음 날 아침 숙취가 현저히 감소함
-간편한 휴대와 섭취 — 작은 스틱 타입이라 가방에 넣기 편하고 물 없이 먹을 수 있음
-고급스러운 선물용 포장 — 리본 손잡이가 달린 쇼핑백 형태 포장이라 선물용으로 우수함</t>
-        </is>
-      </c>
-      <c r="L20" s="3" t="inlineStr">
-        <is>
-          <t>수면 진입 및 숙면 도움 — 자기 전 섭취 시 자연스럽게 졸음이 오고 수면 유지에 도움을 줌
-맛있는 과일 맛 구미 — 상큼한 과일 맛의 젤리 형태로 간식처럼 부담 없이 먹기 좋음</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="60" customHeight="1">
+      <c r="C20" s="3" t="inlineStr"/>
+      <c r="D20" s="3" t="inlineStr"/>
+      <c r="E20" s="3" t="inlineStr"/>
+      <c r="F20" s="3" t="inlineStr"/>
+      <c r="G20" s="3" t="inlineStr"/>
+      <c r="H20" s="3" t="inlineStr"/>
+      <c r="I20" s="3" t="inlineStr"/>
+      <c r="J20" s="3" t="inlineStr"/>
+      <c r="K20" s="3" t="inlineStr"/>
+      <c r="L20" s="3" t="inlineStr"/>
+    </row>
+    <row r="21">
       <c r="B21" s="1" t="inlineStr">
         <is>
           <t>부정리뷰</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>다소 느린 배송 — 배송 도착까지의 시간이 다소 걸림</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>증정품 용량 아쉬움 — 증정으로 제공된 단백질칩의 크기가 다소 작음</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>높은 가격대 — 가격이 다소 비싸 할인 시 구매를 고려하게 됨</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>오배송 및 구성 누락 — 주문한 구성과 다르게 제품이 중복 오배송됨
-포장 터짐 및 누수 — 비닐 포장이 헐겁거나 터져 소스가 새어 나옴</t>
-        </is>
-      </c>
-      <c r="G21" s="3" t="inlineStr">
-        <is>
-          <t>선호 옵션 미포함 — 인기 있는 파우치형 그릴 제품이 구성에 없어 아쉬움</t>
-        </is>
-      </c>
-      <c r="H21" s="3" t="inlineStr">
-        <is>
-          <t>다소 느린 배송 — 배송 도착 속도가 다소 느린 편임</t>
-        </is>
-      </c>
+      <c r="C21" s="3" t="inlineStr"/>
+      <c r="D21" s="3" t="inlineStr"/>
+      <c r="E21" s="3" t="inlineStr"/>
+      <c r="F21" s="3" t="inlineStr"/>
+      <c r="G21" s="3" t="inlineStr"/>
+      <c r="H21" s="3" t="inlineStr"/>
       <c r="I21" s="3" t="inlineStr"/>
       <c r="J21" s="3" t="inlineStr"/>
-      <c r="K21" s="3" t="inlineStr">
-        <is>
-          <t>한약 맛 호불호 — 쌍화탕이나 한약재 특유의 맛이 나 취향을 탈 수 있음</t>
-        </is>
-      </c>
-      <c r="L21" s="3" t="inlineStr">
-        <is>
-          <t>취침 전 당분 부담 — 설탕과 물엿이 함유되어 잠들기 전 섭취 시 당분이 부담스러움</t>
-        </is>
-      </c>
+      <c r="K21" s="3" t="inlineStr"/>
+      <c r="L21" s="3" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="B22" s="1" t="inlineStr">
@@ -4804,17 +4390,17 @@
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
+          <t>18,900원</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
           <t>43,900원</t>
         </is>
       </c>
-      <c r="K22" s="3" t="inlineStr">
+      <c r="L22" s="3" t="inlineStr">
         <is>
           <t>33,200원</t>
-        </is>
-      </c>
-      <c r="L22" s="3" t="inlineStr">
-        <is>
-          <t>18,900원</t>
         </is>
       </c>
     </row>
@@ -5004,7 +4590,7 @@
     <row r="2" ht="38" customHeight="1">
       <c r="B2" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>마그네슘</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -5012,7 +4598,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>대웅제약 녹차 카테킨 6정 6일분</t>
+          <t>대웅제약 마그네슘 30정 30일분</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -5022,48 +4608,36 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000282&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000128&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260504/luK3Rb1JJDaCRTymvaHS600000282_00_01luK3Rb1JJDaCRTymvaHS.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/DZz3h5SxY2J2FqaEB9qZ600000128_00_00DZz3h5SxY2J2FqaEB9qZ.png</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J2" t="n">
-        <v>727</v>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>뛰어난 가성비 — 저렴한 가격으로 가볍게 구매하여 시도하기 좋음</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>적은 칼로리 부담 — 칼로리가 적어 다이어트 중에도 섭취 부담이 없음</t>
-        </is>
-      </c>
+        <v>6520</v>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>미미한 효과 체감 — 섭취 후 별다른 효과를 체감하기 어려움</t>
-        </is>
-      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
     </row>
     <row r="3" ht="38" customHeight="1">
       <c r="B3" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -5071,62 +4645,46 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>[다영 PICK] 셀트리온 다이어트 한 잔 슬림 S 프레소 10포 5일분</t>
+          <t>자연관 이지슬로 엑스트라버진 올리브오일＆레몬 4병</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>셀트리온</t>
+          <t>자연관</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=944863413&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=032627034&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260605/8ADhx4mYwiTujsVcCSTD944863413_00_018ADhx4mYwiTujsVcCSTD.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260810/jotmVom4KndGXbIlPcuj032627034_00_01jotmVom4KndGXbIlPcuj.jpg</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J3" t="n">
-        <v>2719</v>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>커피 대용 활용성 — 카페인 부담이 적어 다이어트 중 커피 대신 마시기 적합함</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>배변 활동 개선 — 꾸준히 마실 경우 변비 해소에 도움을 줌</t>
-        </is>
-      </c>
+        <v>1113</v>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>아쉬운 커피 맛 — 일반 커피에 비해 맛 자체는 다소 아쉬울 수 있음</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>재구매 시 품절 — 제품 구매를 지속하려 할 때 품절 현상이 발생함</t>
-        </is>
-      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
     </row>
     <row r="4" ht="38" customHeight="1">
       <c r="B4" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -5134,45 +4692,37 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>대웅제약 바나바잎 10정 10일분</t>
+          <t>닥터블릿 푸응 7days 팻버닝 21캡슐</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>닥터블릿</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000278&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=613602085&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260504/uooE7Z5tFnMjhhremBna600000278_00_01uooE7Z5tFnMjhhremBna.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260624/m6tznB24o1VYvw4vwVs3613602085_00_00m6tznB24o1VYvw4vwVs3.jpg</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J4" t="n">
-        <v>759</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>식후 속 편안함 — 식후에 복용하면 속이 편안해지며 혈당 관리에 도움을 줌</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>저렴한 가성비 — 가격이 매우 저렴하며 과대 포장이 없어 실용적임</t>
-        </is>
-      </c>
+        <v>2771</v>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -5181,7 +4731,7 @@
     <row r="5" ht="38" customHeight="1">
       <c r="B5" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -5189,54 +4739,46 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>동국 맛있는 샐러드 미니볼 비타 15포 15일분</t>
+          <t>자연관 스파이크컷 바나바잎＆카테킨 4병</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>자연관</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>3,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610910967&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=032627033&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260415/rKimZ2TE65XK1Rwibsnv610910967_00_02rKimZ2TE65XK1Rwibsnv.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260819/2NKz5YxykngJc58J5cja032627033_00_012NKz5YxykngJc58J5cja.jpg</t>
         </is>
       </c>
       <c r="I5" t="n">
         <v>4.8</v>
       </c>
       <c r="J5" t="n">
-        <v>1524</v>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>맛있고 간편한 섭취 — 맛이 좋아 배고플 때 간식 대용으로 편하게 먹기 좋음</t>
-        </is>
-      </c>
+        <v>349</v>
+      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>딱딱한 식감 — 제형이 다소 딱딱하여 씹어 먹기 불편할 수 있음</t>
-        </is>
-      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
     </row>
     <row r="6" ht="38" customHeight="1">
       <c r="B6" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -5244,12 +4786,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>홀베리 유기농 레몬즙 10포</t>
+          <t>[우형재 PICK] 익스트림 모노크레아틴 플러스 120 g 40일분</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>홀베리</t>
+          <t>익스트림</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -5259,30 +4801,22 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=965923434&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=987253276&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260305/6AQS4j3WbfucTbhmJ4ur965923434_00_006AQS4j3WbfucTbhmJ4ur.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260422/qm625V7JKEa8Iu7GrFAf987253276_00_01qm625V7JKEa8Iu7GrFAf.jpg</t>
         </is>
       </c>
       <c r="I6" t="n">
         <v>4.8</v>
       </c>
       <c r="J6" t="n">
-        <v>1625</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>상큼한 맛과 용이성 — 생수에 타서 마시기 좋고 새콤하여 맛이 있음</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>적은 속쓰림 — 병에 든 액상 제품보다 속쓰림 자극이 적음</t>
-        </is>
-      </c>
+        <v>723</v>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -5291,7 +4825,7 @@
     <row r="7" ht="38" customHeight="1">
       <c r="B7" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>루테인/눈건강</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -5299,45 +4833,37 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>동국 맛있는 샐러드 미니볼 15포 15일분</t>
+          <t>종근당건강 혈행건강엔 rTG오메가3 비타민 ADE 30캡슐 30일분</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>종근당건강</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>3,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610910891&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=591581111&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260312/tgDz0oHoOLB3gj3BLgFd610910891_00_01tgDz0oHoOLB3gj3BLgFd.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260424/ryqqbn8htR0Ir3fAZcjp591581111_00_01ryqqbn8htR0Ir3fAZcjp.jpg</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J7" t="n">
-        <v>2245</v>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>편리한 스틱 제형 — 스틱 형태로 개별 포장되어 있어 먹기 편리함</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>씹는 식감과 맛 — 씹어 먹는 재미가 있고 부담 없는 건강한 맛임</t>
-        </is>
-      </c>
+        <v>850</v>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
@@ -5381,27 +4907,19 @@
         <v>4.8</v>
       </c>
       <c r="J8" t="n">
-        <v>1756</v>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>브랜드 신뢰와 가성비 — 믿을 수 있는 브랜드이며 가격 대비 만족도가 높음</t>
-        </is>
-      </c>
+        <v>1757</v>
+      </c>
+      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>즉각적 체감 미흡 — 눈으로 느껴지는 즉각적인 개선 효과 체감은 적음</t>
-        </is>
-      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
     </row>
     <row r="9" ht="38" customHeight="1">
       <c r="B9" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -5409,12 +4927,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>자연관 이뮨 멀티비타민 미네랄 4병</t>
+          <t>LG생활건강 이너뷰 칼륨밸런스 전해질워터 10포</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>자연관</t>
+          <t>이너뷰 바이 리튠</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -5424,35 +4942,23 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=613602124&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=994953534&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20251216/mSQXyRQCV8ORV8edPm4n613602124_00_01mSQXyRQCV8ORV8edPm4n.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250627/7ii4aNyp1XbM6AH8HjHT994953534_00_007ii4aNyp1XbM6AH8HjHT.jpg</t>
         </is>
       </c>
       <c r="I9" t="n">
         <v>4.8</v>
       </c>
       <c r="J9" t="n">
-        <v>1887</v>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>상큼한 맛과 편의성 — 패션후르츠 맛이 나 맛있고 한 병씩 마시기 간편함</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>피로 회복 느낌 — 피곤할 때 섭취 시 활력이 충전되는 느낌을 받음</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>합리적인 가격 — 가성비가 뛰어나 부담 없이 지속 구매 가능함</t>
-        </is>
-      </c>
+        <v>1373</v>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
@@ -5460,7 +4966,7 @@
     <row r="10" ht="38" customHeight="1">
       <c r="B10" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>루테인/눈건강</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -5468,62 +4974,46 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>[정상 면역] 동화약품 배러크런치 아연 청포도맛 30정 10일분</t>
+          <t>안국약품 토비콤 루테인 지아잔틴 24캡슐</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>동화약품</t>
+          <t>안국약품</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>3,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=601678606&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=611982830&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260825/9arKLwQMyanllW5dsWAc601678606_00_029arKLwQMyanllW5dsWAc.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250623/xCRETYTkHbPblUcjT18I611982830_00_00xCRETYTkHbPblUcjT18I.jpg</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="J10" t="n">
-        <v>50</v>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>맛있는 츄어블 제형 — 맛있게 씹어 먹을 수 있어 영양 챙기기 좋음</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>휴대하기 좋은 용기 — 크기가 작고 용기가 예뻐 들고 다니며 먹기 편함</t>
-        </is>
-      </c>
+        <v>1103</v>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>맛에 대한 호불호 — 사람에 따라 맛이 다소 어색하게 느껴질 수 있음</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>효과 체감 미흡 — 제품의 효과를 확실히 느끼기 어려울 수 있음</t>
-        </is>
-      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
     </row>
     <row r="11" ht="38" customHeight="1">
       <c r="B11" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -5531,51 +5021,39 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>대웅제약 맥주효모 비오틴 30정 30일분</t>
+          <t>[김종국 PICK] 익스트림 아르기닌 에너지온 2개입 2일분</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>익스트림</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>1,500원</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000140&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=987253277&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/nz7SB5WS5Csy7uymMIBh600000140_00_00nz7SB5WS5Csy7uymMIBh.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260422/eIhoZ9JSC5jbp33vSbZX987253277_00_01eIhoZ9JSC5jbp33vSbZX.jpg</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J11" t="n">
-        <v>1525</v>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>모발 및 손톱 관리 — 꾸준히 복용 시 머리 빠짐이 줄고 손톱 갈라짐 완화에 도움을 줌</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>부담 없는 가성비 — 가격이 저렴하여 장기 복용 시 부담이 적음</t>
-        </is>
-      </c>
+        <v>809</v>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>효과 체감의 개인차 — 장기간 복용해도 모발이나 손톱 개선 효과를 체감하지 못할 수 있음</t>
-        </is>
-      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
     </row>
@@ -5690,52 +5168,52 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
+          <t>마그네슘</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>다이어트/체중관리</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>다이어트/체중관리</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>루테인/눈건강</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>루테인/눈건강</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>루테인/눈건강</t>
         </is>
       </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>멀티비타민/종합비타민</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
     </row>
@@ -5752,27 +5230,27 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>셀트리온</t>
+          <t>자연관</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>닥터블릿</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>자연관</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>홀베리</t>
+          <t>익스트림</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>종근당건강</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
@@ -5782,17 +5260,17 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>자연관</t>
+          <t>이너뷰 바이 리튠</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>동화약품</t>
+          <t>안국약품</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>익스트림</t>
         </is>
       </c>
     </row>
@@ -5804,32 +5282,32 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>대웅제약 녹차 카테킨 6정 6일분</t>
+          <t>대웅제약 마그네슘 30정 30일분</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>[다영 PICK] 셀트리온 다이어트 한 잔 슬림 S 프레소 10포 5일분</t>
+          <t>자연관 이지슬로 엑스트라버진 올리브오일＆레몬 4병</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>대웅제약 바나바잎 10정 10일분</t>
+          <t>닥터블릿 푸응 7days 팻버닝 21캡슐</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>동국 맛있는 샐러드 미니볼 비타 15포 15일분</t>
+          <t>자연관 스파이크컷 바나바잎＆카테킨 4병</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>홀베리 유기농 레몬즙 10포</t>
+          <t>[우형재 PICK] 익스트림 모노크레아틴 플러스 120 g 40일분</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>동국 맛있는 샐러드 미니볼 15포 15일분</t>
+          <t>종근당건강 혈행건강엔 rTG오메가3 비타민 ADE 30캡슐 30일분</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
@@ -5839,17 +5317,17 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>자연관 이뮨 멀티비타민 미네랄 4병</t>
+          <t>LG생활건강 이너뷰 칼륨밸런스 전해질워터 10포</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>[정상 면역] 동화약품 배러크런치 아연 청포도맛 30정 10일분</t>
+          <t>안국약품 토비콤 루테인 지아잔틴 24캡슐</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>대웅제약 맥주효모 비오틴 30정 30일분</t>
+          <t>[김종국 PICK] 익스트림 아르기닌 에너지온 2개입 2일분</t>
         </is>
       </c>
     </row>
@@ -5860,13 +5338,13 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="E6" s="3" t="n">
         <v>4.7</v>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>4.8</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>4.8</v>
@@ -5875,7 +5353,7 @@
         <v>4.8</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="I6" s="3" t="n">
         <v>4.8</v>
@@ -5884,10 +5362,10 @@
         <v>4.8</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="7">
@@ -5897,144 +5375,69 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>727</v>
+        <v>6520</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>2719</v>
+        <v>1113</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>759</v>
+        <v>2771</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>1524</v>
+        <v>349</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>1625</v>
+        <v>723</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>2245</v>
+        <v>850</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>1756</v>
+        <v>1757</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>1887</v>
+        <v>1373</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>50</v>
+        <v>1103</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>1525</v>
-      </c>
-    </row>
-    <row r="8" ht="90" customHeight="1">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="8">
       <c r="B8" s="1" t="inlineStr">
         <is>
           <t>긍정리뷰</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>뛰어난 가성비 — 저렴한 가격으로 가볍게 구매하여 시도하기 좋음
-적은 칼로리 부담 — 칼로리가 적어 다이어트 중에도 섭취 부담이 없음</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>커피 대용 활용성 — 카페인 부담이 적어 다이어트 중 커피 대신 마시기 적합함
-배변 활동 개선 — 꾸준히 마실 경우 변비 해소에 도움을 줌</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>식후 속 편안함 — 식후에 복용하면 속이 편안해지며 혈당 관리에 도움을 줌
-저렴한 가성비 — 가격이 매우 저렴하며 과대 포장이 없어 실용적임</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>맛있고 간편한 섭취 — 맛이 좋아 배고플 때 간식 대용으로 편하게 먹기 좋음</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>상큼한 맛과 용이성 — 생수에 타서 마시기 좋고 새콤하여 맛이 있음
-적은 속쓰림 — 병에 든 액상 제품보다 속쓰림 자극이 적음</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>편리한 스틱 제형 — 스틱 형태로 개별 포장되어 있어 먹기 편리함
-씹는 식감과 맛 — 씹어 먹는 재미가 있고 부담 없는 건강한 맛임</t>
-        </is>
-      </c>
-      <c r="I8" s="3" t="inlineStr">
-        <is>
-          <t>브랜드 신뢰와 가성비 — 믿을 수 있는 브랜드이며 가격 대비 만족도가 높음</t>
-        </is>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>상큼한 맛과 편의성 — 패션후르츠 맛이 나 맛있고 한 병씩 마시기 간편함
-피로 회복 느낌 — 피곤할 때 섭취 시 활력이 충전되는 느낌을 받음
-합리적인 가격 — 가성비가 뛰어나 부담 없이 지속 구매 가능함</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
-          <t>맛있는 츄어블 제형 — 맛있게 씹어 먹을 수 있어 영양 챙기기 좋음
-휴대하기 좋은 용기 — 크기가 작고 용기가 예뻐 들고 다니며 먹기 편함</t>
-        </is>
-      </c>
-      <c r="L8" s="3" t="inlineStr">
-        <is>
-          <t>모발 및 손톱 관리 — 꾸준히 복용 시 머리 빠짐이 줄고 손톱 갈라짐 완화에 도움을 줌
-부담 없는 가성비 — 가격이 저렴하여 장기 복용 시 부담이 적음</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="60" customHeight="1">
+      <c r="C8" s="3" t="inlineStr"/>
+      <c r="D8" s="3" t="inlineStr"/>
+      <c r="E8" s="3" t="inlineStr"/>
+      <c r="F8" s="3" t="inlineStr"/>
+      <c r="G8" s="3" t="inlineStr"/>
+      <c r="H8" s="3" t="inlineStr"/>
+      <c r="I8" s="3" t="inlineStr"/>
+      <c r="J8" s="3" t="inlineStr"/>
+      <c r="K8" s="3" t="inlineStr"/>
+      <c r="L8" s="3" t="inlineStr"/>
+    </row>
+    <row r="9">
       <c r="B9" s="1" t="inlineStr">
         <is>
           <t>부정리뷰</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>미미한 효과 체감 — 섭취 후 별다른 효과를 체감하기 어려움</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>아쉬운 커피 맛 — 일반 커피에 비해 맛 자체는 다소 아쉬울 수 있음
-재구매 시 품절 — 제품 구매를 지속하려 할 때 품절 현상이 발생함</t>
-        </is>
-      </c>
+      <c r="C9" s="3" t="inlineStr"/>
+      <c r="D9" s="3" t="inlineStr"/>
       <c r="E9" s="3" t="inlineStr"/>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>딱딱한 식감 — 제형이 다소 딱딱하여 씹어 먹기 불편할 수 있음</t>
-        </is>
-      </c>
+      <c r="F9" s="3" t="inlineStr"/>
       <c r="G9" s="3" t="inlineStr"/>
       <c r="H9" s="3" t="inlineStr"/>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>즉각적 체감 미흡 — 눈으로 느껴지는 즉각적인 개선 효과 체감은 적음</t>
-        </is>
-      </c>
+      <c r="I9" s="3" t="inlineStr"/>
       <c r="J9" s="3" t="inlineStr"/>
-      <c r="K9" s="3" t="inlineStr">
-        <is>
-          <t>맛에 대한 호불호 — 사람에 따라 맛이 다소 어색하게 느껴질 수 있음
-효과 체감 미흡 — 제품의 효과를 확실히 느끼기 어려울 수 있음</t>
-        </is>
-      </c>
-      <c r="L9" s="3" t="inlineStr">
-        <is>
-          <t>효과 체감의 개인차 — 장기간 복용해도 모발이나 손톱 개선 효과를 체감하지 못할 수 있음</t>
-        </is>
-      </c>
+      <c r="K9" s="3" t="inlineStr"/>
+      <c r="L9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="B10" s="1" t="inlineStr">
@@ -6044,22 +5447,22 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>1,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>2,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>1,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>3,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
@@ -6069,7 +5472,7 @@
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>3,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
@@ -6084,12 +5487,12 @@
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>3,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>1,500원</t>
         </is>
       </c>
     </row>
@@ -6268,7 +5671,7 @@
     <row r="2" ht="38" customHeight="1">
       <c r="B2" t="inlineStr">
         <is>
-          <t>비타민C/항산화</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -6276,27 +5679,27 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>고려은단 비타민C1000 600정 (20개월분)</t>
+          <t>판도라 브이트리티 7/14+1포 (7/15일분)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>고려은단</t>
+          <t>판도라</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>42,900원</t>
+          <t>24,200원</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000225938&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=1</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000227334&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=1</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022593803ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022733453ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -6311,7 +5714,7 @@
     <row r="3" ht="38" customHeight="1">
       <c r="B3" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>비타민C/항산화</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -6319,31 +5722,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>판도라 브이트리티 7/14+1포 (7/15일분)</t>
+          <t>고려은단 비타민C1000 600정 (20개월분)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>판도라</t>
+          <t>고려은단</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>24,200원</t>
+          <t>42,900원</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000227334&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=2</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000225938&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=2</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022733453ko.jpg?l=ko</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022593803ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J3" t="n">
+        <v>22349</v>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
@@ -6354,7 +5761,7 @@
     <row r="4" ht="38" customHeight="1">
       <c r="B4" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -6362,46 +5769,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>[한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
+          <t>[곽민경 PICK] 생활약속 기분전환 알파플러스 10포 (+1포 증정기획)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>프로뉴트리션</t>
+          <t>생활약속</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>35,800원</t>
+          <t>16,200원</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000205496&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=3</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000180121&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=3</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020549614ko.jpg?l=ko</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>장 및 체지방 이중 관리 — 장 건강과 체지방 감소를 한 번에 케어할 수 있음</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>상큼한 요거트 맛 — 요거트 맛으로 맛있게 하루 한 포씩 먹기 좋음</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>속 편안함 제공 — 섭취 후 아랫배 더부룩함 없이 속을 편안하게 해줌</t>
-        </is>
-      </c>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0018/A00000018012128ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J4" t="n">
+        <v>17077</v>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
@@ -6417,47 +5816,39 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>[감자숭이 기획] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
+          <t>[TWS 띠부씰 증정] 미에로화이바 브이캔디 20정 기획</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>멜라메이트</t>
+          <t>미에로화이바</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>16,900원</t>
+          <t>9,900원</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000223554&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=4</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000268343&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=4</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022355477ko.jpg?l=ko</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>빠른 숙면 유도 — 자기 전 먹으면 빠르고 깊게 잠드는 데 효과적임</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>편리하고 맛있는 구미 — 맛있는 젤리 형태라 물 없이 머리맡에 두고 섭취하기 좋음</t>
-        </is>
-      </c>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0026/A00000026834303ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>5</v>
+      </c>
+      <c r="J5" t="n">
+        <v>12</v>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>섭취 후 양치 필요 — 자기 전 젤리 섭취 후 양치를 다시 해야 하는 번거로움이 존재함</t>
-        </is>
-      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
     </row>
@@ -6472,31 +5863,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>[9월 올영픽/산리오콜라보] CJ 바이오코어 유산균 3종 (피부/다이어트/500억) (+산리오 러기지택)</t>
+          <t>[한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>바이오코어유산균</t>
+          <t>프로뉴트리션</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>13,950원</t>
+          <t>35,800원</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000200143&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=5</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000205496&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=5</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020014345ko.jpg?l=ko</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020549614ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J6" t="n">
+        <v>543</v>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
@@ -6515,31 +5910,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>[TWS 띠부씰 증정] 미에로화이바 브이캔디 20정 기획</t>
+          <t>[감자숭이 기획] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>미에로화이바</t>
+          <t>멜라메이트</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>9,900원</t>
+          <t>16,900원</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000268343&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=6</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000223554&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=6</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0026/A00000026834303ko.jpg?l=ko</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022355477ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J7" t="n">
+        <v>15734</v>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
@@ -6550,7 +5949,7 @@
     <row r="8" ht="38" customHeight="1">
       <c r="B8" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -6558,27 +5957,27 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>[곽민경 PICK] 생활약속 기분전환 알파플러스 10포 (+1포 증정기획)</t>
+          <t>[9월 올영픽/산리오콜라보] CJ 바이오코어 유산균 3종 (피부/다이어트/500억) (+산리오 러기지택)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>생활약속</t>
+          <t>바이오코어유산균</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>16,200원</t>
+          <t>13,950원</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000180121&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=7</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000200143&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=7</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0018/A00000018012128ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020014345ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -6593,7 +5992,7 @@
     <row r="9" ht="38" customHeight="1">
       <c r="B9" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -6601,31 +6000,35 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>[골라담기] CJ웰케어 건강루틴 가격혁명 12종 택 1</t>
+          <t>탄탄 더블컷 다이어트 젤리 2종 택1 (자두맛/애플유자맛)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>씨제이웰케어</t>
+          <t>탄탄</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>5,900원</t>
+          <t>8,900원</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000247861&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=8</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000213057&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=8</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024786106ko.jpg?l=ko</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0021/A00000021305744ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J9" t="n">
+        <v>6074</v>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
@@ -6636,7 +6039,7 @@
     <row r="10" ht="38" customHeight="1">
       <c r="B10" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -6644,34 +6047,34 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>[덴마크 직수입]덴프스 덴마크 유산균이야기 30캡슐(1개월분)</t>
+          <t>콜레올로지 컷팅 젤리 레몬/키위/석류 10+2+2포 기획 외</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>덴프스</t>
+          <t>푸드올로지</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>17,960원</t>
+          <t>18,800원</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000189360&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=9</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000183645&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=9</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0018/A00000018936006ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0018/A00000018364590ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I10" t="n">
         <v>4.8</v>
       </c>
       <c r="J10" t="n">
-        <v>2626</v>
+        <v>31327</v>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
@@ -6691,31 +6094,35 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>[딥트3일/남규리PICK]남규리의 바른 효소 리셋 8포</t>
+          <t>[골라담기] CJ웰케어 건강루틴 가격혁명 12종 택 1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>딥트3일</t>
+          <t>씨제이웰케어</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>11,400원</t>
+          <t>5,900원</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000211396&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=10</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000247861&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=10</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0021/A00000021139617ko.jpg?l=ko</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024786106ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J11" t="n">
+        <v>19308</v>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
@@ -6834,47 +6241,47 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
           <t>비타민C/항산화</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>다이어트/체중관리</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>다이어트/체중관리</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
@@ -6891,52 +6298,52 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
+          <t>판도라</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
           <t>고려은단</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>판도라</t>
-        </is>
-      </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
+          <t>생활약속</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>미에로화이바</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
           <t>프로뉴트리션</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>멜라메이트</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>바이오코어유산균</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>미에로화이바</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>생활약속</t>
-        </is>
-      </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
+          <t>탄탄</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>푸드올로지</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
           <t>씨제이웰케어</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>덴프스</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>딥트3일</t>
         </is>
       </c>
     </row>
@@ -6948,52 +6355,52 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
+          <t>판도라 브이트리티 7/14+1포 (7/15일분)</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
           <t>고려은단 비타민C1000 600정 (20개월분)</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>판도라 브이트리티 7/14+1포 (7/15일분)</t>
-        </is>
-      </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
+          <t>[곽민경 PICK] 생활약속 기분전환 알파플러스 10포 (+1포 증정기획)</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>[TWS 띠부씰 증정] 미에로화이바 브이캔디 20정 기획</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
           <t>[한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>[감자숭이 기획] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>[9월 올영픽/산리오콜라보] CJ 바이오코어 유산균 3종 (피부/다이어트/500억) (+산리오 러기지택)</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>[TWS 띠부씰 증정] 미에로화이바 브이캔디 20정 기획</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>[곽민경 PICK] 생활약속 기분전환 알파플러스 10포 (+1포 증정기획)</t>
-        </is>
-      </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
+          <t>탄탄 더블컷 다이어트 젤리 2종 택1 (자두맛/애플유자맛)</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>콜레올로지 컷팅 젤리 레몬/키위/석류 10+2+2포 기획 외</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
           <t>[골라담기] CJ웰케어 건강루틴 가격혁명 12종 택 1</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>[덴마크 직수입]덴프스 덴마크 유산균이야기 30캡슐(1개월분)</t>
-        </is>
-      </c>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t>[딥트3일/남규리PICK]남규리의 바른 효소 리셋 8포</t>
         </is>
       </c>
     </row>
@@ -7004,17 +6411,31 @@
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr"/>
-      <c r="D6" s="3" t="inlineStr"/>
-      <c r="E6" s="3" t="inlineStr"/>
-      <c r="F6" s="3" t="inlineStr"/>
-      <c r="G6" s="3" t="inlineStr"/>
-      <c r="H6" s="3" t="inlineStr"/>
+      <c r="D6" s="3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>4.8</v>
+      </c>
       <c r="I6" s="3" t="inlineStr"/>
-      <c r="J6" s="3" t="inlineStr"/>
+      <c r="J6" s="3" t="n">
+        <v>4.8</v>
+      </c>
       <c r="K6" s="3" t="n">
         <v>4.8</v>
       </c>
-      <c r="L6" s="3" t="inlineStr"/>
+      <c r="L6" s="3" t="n">
+        <v>4.8</v>
+      </c>
     </row>
     <row r="7">
       <c r="B7" s="1" t="inlineStr">
@@ -7023,19 +6444,33 @@
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr"/>
-      <c r="D7" s="3" t="inlineStr"/>
-      <c r="E7" s="3" t="inlineStr"/>
-      <c r="F7" s="3" t="inlineStr"/>
-      <c r="G7" s="3" t="inlineStr"/>
-      <c r="H7" s="3" t="inlineStr"/>
+      <c r="D7" s="3" t="n">
+        <v>22349</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>17077</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>543</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>15734</v>
+      </c>
       <c r="I7" s="3" t="inlineStr"/>
-      <c r="J7" s="3" t="inlineStr"/>
+      <c r="J7" s="3" t="n">
+        <v>6074</v>
+      </c>
       <c r="K7" s="3" t="n">
-        <v>2626</v>
-      </c>
-      <c r="L7" s="3" t="inlineStr"/>
-    </row>
-    <row r="8" ht="90" customHeight="1">
+        <v>31327</v>
+      </c>
+      <c r="L7" s="3" t="n">
+        <v>19308</v>
+      </c>
+    </row>
+    <row r="8">
       <c r="B8" s="1" t="inlineStr">
         <is>
           <t>긍정리뷰</t>
@@ -7043,19 +6478,8 @@
       </c>
       <c r="C8" s="3" t="inlineStr"/>
       <c r="D8" s="3" t="inlineStr"/>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>장 및 체지방 이중 관리 — 장 건강과 체지방 감소를 한 번에 케어할 수 있음
-상큼한 요거트 맛 — 요거트 맛으로 맛있게 하루 한 포씩 먹기 좋음
-속 편안함 제공 — 섭취 후 아랫배 더부룩함 없이 속을 편안하게 해줌</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>빠른 숙면 유도 — 자기 전 먹으면 빠르고 깊게 잠드는 데 효과적임
-편리하고 맛있는 구미 — 맛있는 젤리 형태라 물 없이 머리맡에 두고 섭취하기 좋음</t>
-        </is>
-      </c>
+      <c r="E8" s="3" t="inlineStr"/>
+      <c r="F8" s="3" t="inlineStr"/>
       <c r="G8" s="3" t="inlineStr"/>
       <c r="H8" s="3" t="inlineStr"/>
       <c r="I8" s="3" t="inlineStr"/>
@@ -7072,11 +6496,7 @@
       <c r="C9" s="3" t="inlineStr"/>
       <c r="D9" s="3" t="inlineStr"/>
       <c r="E9" s="3" t="inlineStr"/>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>섭취 후 양치 필요 — 자기 전 젤리 섭취 후 양치를 다시 해야 하는 번거로움이 존재함</t>
-        </is>
-      </c>
+      <c r="F9" s="3" t="inlineStr"/>
       <c r="G9" s="3" t="inlineStr"/>
       <c r="H9" s="3" t="inlineStr"/>
       <c r="I9" s="3" t="inlineStr"/>
@@ -7092,52 +6512,52 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
+          <t>24,200원</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
           <t>42,900원</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>24,200원</t>
-        </is>
-      </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
+          <t>16,200원</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>9,900원</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
           <t>35,800원</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="H10" s="3" t="inlineStr">
         <is>
           <t>16,900원</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="I10" s="3" t="inlineStr">
         <is>
           <t>13,950원</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>9,900원</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>16,200원</t>
-        </is>
-      </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
+          <t>8,900원</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>18,800원</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
           <t>5,900원</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t>17,960원</t>
-        </is>
-      </c>
-      <c r="L10" s="3" t="inlineStr">
-        <is>
-          <t>11,400원</t>
         </is>
       </c>
     </row>
@@ -7263,45 +6683,45 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C2" t="n">
-        <v>37.5</v>
+        <v>32.5</v>
       </c>
       <c r="D2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F2" t="n">
         <v>4</v>
-      </c>
-      <c r="E2" t="n">
-        <v>5</v>
-      </c>
-      <c r="F2" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C3" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
@@ -7311,16 +6731,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C4" t="n">
-        <v>22.5</v>
+        <v>20</v>
       </c>
       <c r="D4" t="n">
         <v>8</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -7329,20 +6749,20 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>루테인/눈건강</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>7.5</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -7351,7 +6771,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>루테인/눈건강</t>
+          <t>비타민C/항산화</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -7364,16 +6784,16 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
         <v>1</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>홍삼/인삼</t>
+          <t>마그네슘</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -7383,10 +6803,10 @@
         <v>2.5</v>
       </c>
       <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
         <v>1</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -7395,7 +6815,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>비타민C/항산화</t>
+          <t>피부/미용</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -7405,19 +6825,19 @@
         <v>2.5</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>홍삼/인삼</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -7427,13 +6847,13 @@
         <v>2.5</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
